--- a/contractor_forms/002_pricing_estimation_survey--contractor_forms.xlsx
+++ b/contractor_forms/002_pricing_estimation_survey--contractor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'less_than_1000'}</t>
+          <t>less_than_1000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Less than 1000'}</t>
+          <t>Less than 1000</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'1000_-_2000'}</t>
+          <t>1000_-_2000</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': '1000 - 2000'}</t>
+          <t>1000 - 2000</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'2000_-_3000'}</t>
+          <t>2000_-_3000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': '2000 - 3000'}</t>
+          <t>2000 - 3000</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'more_than_3000'}</t>
+          <t>more_than_3000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'More than 3000'}</t>
+          <t>More than 3000</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'residential'}</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Residential'}</t>
+          <t>Residential</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Commercial'}</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'fixed'}</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Fixed'}</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'cost_plus'}</t>
+          <t>cost_plus</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Cost Plus'}</t>
+          <t>Cost Plus</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'time_and_materials'}</t>
+          <t>time_and_materials</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Time and Materials'}</t>
+          <t>Time and Materials</t>
         </is>
       </c>
     </row>
